--- a/support-pulse/support_pulse.xlsx
+++ b/support-pulse/support_pulse.xlsx
@@ -5903,7 +5903,7 @@
         <v>3</v>
       </c>
       <c r="S89" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="90">
@@ -5929,10 +5929,10 @@
         <v>41</v>
       </c>
       <c r="F90" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G90" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I90" t="n">
         <v>5</v>
@@ -5956,16 +5956,16 @@
         <v>6</v>
       </c>
       <c r="P90" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>29.4</v>
+        <v>28.7</v>
       </c>
       <c r="S90" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="91">
@@ -5988,13 +5988,13 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -6018,10 +6018,16 @@
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -6983,13 +6989,13 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I15" t="n">
         <v>6</v>
@@ -7013,16 +7019,16 @@
         <v>9</v>
       </c>
       <c r="P15" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>18.9</v>
+        <v>17.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -7364,13 +7370,13 @@
         <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
@@ -7394,7 +7400,7 @@
         <v>31</v>
       </c>
       <c r="P5" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="Q5" t="n">
         <v>12.9</v>
@@ -7403,7 +7409,7 @@
         <v>10.1</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>

--- a/support-pulse/support_pulse.xlsx
+++ b/support-pulse/support_pulse.xlsx
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -658,16 +658,10 @@
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="S3" t="n">
-        <v>36.6</v>
       </c>
     </row>
     <row r="4">
@@ -2432,7 +2426,7 @@
         <v>966.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="33">
@@ -2839,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -5177,7 +5171,7 @@
         <v>34.7</v>
       </c>
       <c r="S77" t="n">
-        <v>3.9</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="78">
@@ -5324,13 +5318,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -5354,10 +5348,16 @@
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>114</v>
+      </c>
+      <c r="S80" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -5534,7 +5534,7 @@
         <v>33.3</v>
       </c>
       <c r="R83" t="n">
-        <v>3.2</v>
+        <v>176.8</v>
       </c>
       <c r="S83" t="n">
         <v>3.9</v>
@@ -5661,7 +5661,7 @@
         <v>6.8</v>
       </c>
       <c r="S85" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="86">
@@ -5720,7 +5720,7 @@
         <v>14.3</v>
       </c>
       <c r="R86" t="n">
-        <v>2.1</v>
+        <v>171.3</v>
       </c>
       <c r="S86" t="n">
         <v>2.6</v>
@@ -5841,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="89">
@@ -5903,7 +5903,7 @@
         <v>3</v>
       </c>
       <c r="S89" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="90">
@@ -5962,10 +5962,10 @@
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>28.7</v>
+        <v>35.8</v>
       </c>
       <c r="S90" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="91">
@@ -5985,28 +5985,28 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
+        <v>21</v>
+      </c>
+      <c r="F91" t="n">
+        <v>19</v>
+      </c>
+      <c r="G91" t="n">
+        <v>44</v>
+      </c>
+      <c r="I91" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" t="n">
-        <v>6</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -6015,19 +6015,19 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="S91" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -6183,13 +6183,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -6213,16 +6213,16 @@
         <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
         <v>14.3</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>24.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="3">
@@ -6470,7 +6470,7 @@
         <v>275.7</v>
       </c>
       <c r="S6" t="n">
-        <v>28.4</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="7">
@@ -6508,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>10</v>
@@ -6865,13 +6865,13 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I13" t="n">
         <v>32</v>
@@ -6895,16 +6895,16 @@
         <v>48</v>
       </c>
       <c r="P13" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="n">
         <v>14.6</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>13.9</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="14">
@@ -6963,10 +6963,10 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>5.6</v>
+        <v>71.7</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="15">
@@ -6986,28 +6986,28 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>87</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56</v>
+      </c>
+      <c r="G15" t="n">
+        <v>151</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>69</v>
-      </c>
-      <c r="F15" t="n">
-        <v>40</v>
-      </c>
-      <c r="G15" t="n">
-        <v>113</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -7016,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="S15" t="n">
         <v>1.9</v>
@@ -7184,13 +7184,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I2" t="n">
         <v>19</v>
@@ -7214,16 +7214,16 @@
         <v>40</v>
       </c>
       <c r="P2" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q2" t="n">
         <v>17.5</v>
       </c>
       <c r="R2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="S2" t="n">
         <v>33.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="3">
@@ -7261,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>58</v>
@@ -7285,7 +7285,7 @@
         <v>117.2</v>
       </c>
       <c r="S3" t="n">
-        <v>40.5</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="4">
@@ -7308,13 +7308,13 @@
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G4" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="I4" t="n">
         <v>68</v>
@@ -7338,16 +7338,16 @@
         <v>128</v>
       </c>
       <c r="P4" t="n">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="Q4" t="n">
         <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>61.8</v>
+        <v>62.1</v>
       </c>
       <c r="S4" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -7367,28 +7367,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="G5" t="n">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -7397,16 +7397,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P5" t="n">
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.9</v>
+        <v>10.5</v>
       </c>
       <c r="R5" t="n">
-        <v>10.1</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
         <v>3.6</v>

--- a/support-pulse/support_pulse.xlsx
+++ b/support-pulse/support_pulse.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5965,7 +5965,7 @@
         <v>35.8</v>
       </c>
       <c r="S90" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="91">
@@ -5985,19 +5985,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G91" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -6015,19 +6015,137 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P91" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.6</v>
+        <v>20.7</v>
       </c>
       <c r="S91" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>10</v>
+      </c>
+      <c r="F92" t="n">
+        <v>11</v>
+      </c>
+      <c r="G92" t="n">
+        <v>23</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>3</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>2</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6986,19 +7104,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7007,7 +7125,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -7016,19 +7134,19 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>17</v>
+        <v>19.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
@@ -7367,19 +7485,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
+        <v>171</v>
+      </c>
+      <c r="F5" t="n">
         <v>158</v>
       </c>
-      <c r="F5" t="n">
-        <v>141</v>
-      </c>
       <c r="G5" t="n">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -7388,7 +7506,7 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -7397,19 +7515,19 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="P5" t="n">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="R5" t="n">
-        <v>47.6</v>
+        <v>45.7</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/support-pulse/support_pulse.xlsx
+++ b/support-pulse/support_pulse.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily'!$A$1:$S$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly'!$A$1:$S$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily'!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly'!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly'!$A$1:$T$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:T93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,55 +499,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>No-effort closes (fast/spam/no-reply)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>CUS created</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CUS P0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CUS P1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>REP created</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>REP P0</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>REP P1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Linear total</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Grand total</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>1 Metric: created+completed ≤7d (%)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Avg 1st response (min)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Avg resolution (hrs)</t>
         </is>
@@ -580,9 +586,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -590,21 +593,24 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -636,31 +642,31 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
       </c>
       <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -692,37 +698,37 @@
       <c r="G4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.6</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -754,9 +760,6 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -776,12 +779,15 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>5.5</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>35</v>
       </c>
     </row>
@@ -835,12 +841,15 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
       <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
         <v>35</v>
       </c>
     </row>
@@ -873,10 +882,10 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -891,18 +900,21 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>9</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.6</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>32.7</v>
       </c>
     </row>
@@ -935,11 +947,11 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
@@ -953,18 +965,21 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>11</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>50</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>1.8</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>20.8</v>
       </c>
     </row>
@@ -997,36 +1012,39 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>11</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>0.6</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>44</v>
       </c>
     </row>
@@ -1059,36 +1077,39 @@
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>13</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>33.3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -1121,7 +1142,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1130,27 +1151,30 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>8</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>68.2</v>
       </c>
     </row>
@@ -1192,21 +1216,24 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1239,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1260,9 +1287,12 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
@@ -1295,7 +1325,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1304,27 +1334,30 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>12</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.9</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>61.7</v>
       </c>
     </row>
@@ -1360,33 +1393,36 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>5</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>7</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>19</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>14.3</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>8.9</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -1419,36 +1455,39 @@
         <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>21</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.7</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>50.1</v>
       </c>
     </row>
@@ -1481,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1490,27 +1529,30 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>22</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>229.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>14.4</v>
       </c>
     </row>
@@ -1543,10 +1585,10 @@
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1561,18 +1603,21 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1605,7 +1650,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1626,12 +1671,15 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>3.6</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1685,12 +1733,15 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>10</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -1723,36 +1774,39 @@
         <v>22</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>25</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>33.3</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>25.8</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>45.2</v>
       </c>
     </row>
@@ -1785,36 +1839,39 @@
         <v>25</v>
       </c>
       <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
         <v>3</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>4</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>29</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>25</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>10.7</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>51.7</v>
       </c>
     </row>
@@ -1847,7 +1904,7 @@
         <v>13</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1856,27 +1913,30 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>3</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>3</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>16</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.5</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>49.6</v>
       </c>
     </row>
@@ -1909,7 +1969,7 @@
         <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1918,27 +1978,30 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>19</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>100</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>1.5</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>72.90000000000001</v>
       </c>
     </row>
@@ -1980,27 +2043,30 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>3</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>9</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>0.4</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -2033,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2042,24 +2108,27 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>6</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>35.5</v>
       </c>
     </row>
@@ -2092,7 +2161,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2113,9 +2182,12 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>4</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>67.40000000000001</v>
       </c>
     </row>
@@ -2148,37 +2220,40 @@
         <v>25</v>
       </c>
       <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>5</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>30</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.2</v>
       </c>
-      <c r="S28" t="n">
-        <v>16.2</v>
+      <c r="T28" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="29">
@@ -2210,36 +2285,39 @@
         <v>23</v>
       </c>
       <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>4</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>27</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>1.5</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>94.90000000000001</v>
       </c>
     </row>
@@ -2272,36 +2350,39 @@
         <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>3</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>22</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>5.7</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -2337,33 +2418,36 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>4</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>5</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>24</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>20</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>4.3</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>11.4</v>
       </c>
     </row>
@@ -2396,11 +2480,11 @@
         <v>39</v>
       </c>
       <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
@@ -2414,18 +2498,21 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>41</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>966.2</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -2458,10 +2545,10 @@
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2476,18 +2563,21 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
         <v>5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>538.6</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>206.6</v>
       </c>
     </row>
@@ -2520,7 +2610,7 @@
         <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2541,12 +2631,15 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>6</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>694.2</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>12.1</v>
       </c>
     </row>
@@ -2579,7 +2672,7 @@
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2588,27 +2681,30 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
         <v>17</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>124.6</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>41.9</v>
       </c>
     </row>
@@ -2641,36 +2737,39 @@
         <v>12</v>
       </c>
       <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
         <v>3</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
         <v>5</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>8</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>20</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>25</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>4</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>38.1</v>
       </c>
     </row>
@@ -2703,36 +2802,39 @@
         <v>15</v>
       </c>
       <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>2</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>3</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>18</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>33.3</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>1.2</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>61.6</v>
       </c>
     </row>
@@ -2765,36 +2867,39 @@
         <v>13</v>
       </c>
       <c r="I38" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>8</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>21</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>43.9</v>
       </c>
     </row>
@@ -2827,36 +2932,39 @@
         <v>12</v>
       </c>
       <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
         <v>7</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>8</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>20</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>0.7</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>43.2</v>
       </c>
     </row>
@@ -2889,7 +2997,7 @@
         <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2898,27 +3006,30 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>6.9</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>61.4</v>
       </c>
     </row>
@@ -2951,36 +3062,39 @@
         <v>20</v>
       </c>
       <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
         <v>2</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>6</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>8</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>28</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>16.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>49.9</v>
       </c>
     </row>
@@ -3013,36 +3127,39 @@
         <v>26</v>
       </c>
       <c r="I42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" t="n">
         <v>5</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>6</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>32</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>141.1</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>51.3</v>
       </c>
     </row>
@@ -3078,33 +3195,36 @@
         <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>4</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>27</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>4.5</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>44.7</v>
       </c>
     </row>
@@ -3137,36 +3257,39 @@
         <v>21</v>
       </c>
       <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
         <v>5</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>7</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>12</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>33</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>16.7</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>3.5</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>49</v>
       </c>
     </row>
@@ -3199,36 +3322,39 @@
         <v>15</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>3</v>
       </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>4</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>19</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>25</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>340.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>33</v>
       </c>
     </row>
@@ -3261,7 +3387,7 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3270,24 +3396,27 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
         <v>38.9</v>
       </c>
     </row>
@@ -3320,7 +3449,7 @@
         <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3341,12 +3470,15 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>10</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>52.5</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>54.5</v>
       </c>
     </row>
@@ -3379,36 +3511,39 @@
         <v>29</v>
       </c>
       <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
         <v>3</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
         <v>4</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>33</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>18.8</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>48</v>
       </c>
     </row>
@@ -3441,36 +3576,39 @@
         <v>22</v>
       </c>
       <c r="I49" t="n">
+        <v>9</v>
+      </c>
+      <c r="J49" t="n">
         <v>7</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>8</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>30</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>15.2</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>35.1</v>
       </c>
     </row>
@@ -3503,36 +3641,39 @@
         <v>11</v>
       </c>
       <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
         <v>6</v>
       </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>2</v>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>8</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>19</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>12.5</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>6.8</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>35.2</v>
       </c>
     </row>
@@ -3565,36 +3706,39 @@
         <v>13</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>6</v>
       </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
         <v>7</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>20</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>42.9</v>
       </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
       <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
         <v>30.6</v>
       </c>
     </row>
@@ -3627,36 +3771,39 @@
         <v>12</v>
       </c>
       <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
         <v>2</v>
       </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
         <v>6</v>
       </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
         <v>8</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>20</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>37.5</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>2</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>18.3</v>
       </c>
     </row>
@@ -3689,7 +3836,7 @@
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3710,9 +3857,12 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>2</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>57.4</v>
       </c>
     </row>
@@ -3745,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3766,9 +3916,12 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
         <v>4</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>28.9</v>
       </c>
     </row>
@@ -3801,36 +3954,39 @@
         <v>20</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
         <v>2</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>22</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>50</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>1.3</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>16.5</v>
       </c>
     </row>
@@ -3863,36 +4019,39 @@
         <v>31</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>2</v>
       </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
         <v>3</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>34</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>33.3</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
       <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
         <v>26.9</v>
       </c>
     </row>
@@ -3925,37 +4084,40 @@
         <v>28</v>
       </c>
       <c r="I57" t="n">
+        <v>9</v>
+      </c>
+      <c r="J57" t="n">
         <v>4</v>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>3</v>
       </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
         <v>7</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>35</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>2.4</v>
       </c>
-      <c r="S57" t="n">
-        <v>39.6</v>
+      <c r="T57" t="n">
+        <v>40.6</v>
       </c>
     </row>
     <row r="58">
@@ -3987,36 +4149,39 @@
         <v>24</v>
       </c>
       <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>3</v>
       </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
         <v>5</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>29</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>20</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>11.6</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>11.7</v>
       </c>
     </row>
@@ -4049,36 +4214,39 @@
         <v>23</v>
       </c>
       <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
         <v>2</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>2</v>
       </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>4</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>27</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>17.5</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>23.4</v>
       </c>
     </row>
@@ -4111,7 +4279,7 @@
         <v>10</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4132,12 +4300,15 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
         <v>10</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>3194.8</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>32.1</v>
       </c>
     </row>
@@ -4170,7 +4341,7 @@
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -4191,12 +4362,15 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="R61" t="n">
+      <c r="S61" t="n">
         <v>4.3</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>13.1</v>
       </c>
     </row>
@@ -4229,36 +4403,39 @@
         <v>25</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
         <v>2</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>27</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>297.1</v>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -4291,36 +4468,39 @@
         <v>20</v>
       </c>
       <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
         <v>3</v>
       </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
         <v>5</v>
       </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
         <v>25</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="R63" t="n">
         <v>20</v>
       </c>
-      <c r="R63" t="n">
+      <c r="S63" t="n">
         <v>149.9</v>
       </c>
-      <c r="S63" t="n">
+      <c r="T63" t="n">
         <v>24.9</v>
       </c>
     </row>
@@ -4353,36 +4533,39 @@
         <v>18</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
         <v>2</v>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>20</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
         <v>50.9</v>
       </c>
-      <c r="S64" t="n">
+      <c r="T64" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4415,37 +4598,40 @@
         <v>24</v>
       </c>
       <c r="I65" t="n">
+        <v>8</v>
+      </c>
+      <c r="J65" t="n">
         <v>3</v>
       </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>7</v>
       </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
         <v>10</v>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>34</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="R65" t="n">
         <v>20</v>
       </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
         <v>1.5</v>
       </c>
-      <c r="S65" t="n">
-        <v>16.6</v>
+      <c r="T65" t="n">
+        <v>27.4</v>
       </c>
     </row>
     <row r="66">
@@ -4477,36 +4663,39 @@
         <v>21</v>
       </c>
       <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
         <v>2</v>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>3</v>
       </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
         <v>5</v>
       </c>
-      <c r="P66" t="n">
+      <c r="Q66" t="n">
         <v>26</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
         <v>3.5</v>
       </c>
-      <c r="S66" t="n">
+      <c r="T66" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4539,7 +4728,7 @@
         <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4560,9 +4749,12 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
         <v>4</v>
       </c>
-      <c r="S67" t="n">
+      <c r="T67" t="n">
         <v>43.4</v>
       </c>
     </row>
@@ -4595,36 +4787,39 @@
         <v>17</v>
       </c>
       <c r="I68" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" t="n">
         <v>2</v>
       </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
         <v>3</v>
       </c>
-      <c r="P68" t="n">
+      <c r="Q68" t="n">
         <v>20</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="R68" t="n">
         <v>33.3</v>
       </c>
-      <c r="R68" t="n">
+      <c r="S68" t="n">
         <v>15.9</v>
       </c>
-      <c r="S68" t="n">
+      <c r="T68" t="n">
         <v>19.8</v>
       </c>
     </row>
@@ -4657,11 +4852,11 @@
         <v>20</v>
       </c>
       <c r="I69" t="n">
+        <v>6</v>
+      </c>
+      <c r="J69" t="n">
         <v>7</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
@@ -4675,18 +4870,21 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>7</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>27</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
         <v>139.3</v>
       </c>
-      <c r="S69" t="n">
+      <c r="T69" t="n">
         <v>18.4</v>
       </c>
     </row>
@@ -4719,36 +4917,39 @@
         <v>21</v>
       </c>
       <c r="I70" t="n">
+        <v>9</v>
+      </c>
+      <c r="J70" t="n">
         <v>2</v>
       </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>5</v>
       </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
         <v>7</v>
       </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
         <v>28</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
         <v>1.2</v>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="n">
         <v>10.2</v>
       </c>
     </row>
@@ -4781,36 +4982,39 @@
         <v>16</v>
       </c>
       <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
         <v>3</v>
       </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
         <v>7</v>
       </c>
-      <c r="P71" t="n">
+      <c r="Q71" t="n">
         <v>23</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="R71" t="n">
         <v>14.3</v>
       </c>
-      <c r="R71" t="n">
+      <c r="S71" t="n">
         <v>2.5</v>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="n">
         <v>21.3</v>
       </c>
     </row>
@@ -4843,7 +5047,7 @@
         <v>9</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4852,27 +5056,30 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>3</v>
       </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
         <v>3</v>
       </c>
-      <c r="P72" t="n">
+      <c r="Q72" t="n">
         <v>12</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
         <v>1.8</v>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="n">
         <v>28.3</v>
       </c>
     </row>
@@ -4905,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4926,9 +5133,12 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
         <v>11.5</v>
       </c>
     </row>
@@ -4961,7 +5171,7 @@
         <v>5</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4982,9 +5192,12 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
         <v>5</v>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
         <v>10.4</v>
       </c>
     </row>
@@ -5017,7 +5230,7 @@
         <v>8</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -5026,27 +5239,30 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
         <v>9</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="R75" t="n">
         <v>100</v>
       </c>
-      <c r="R75" t="n">
+      <c r="S75" t="n">
         <v>5</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>12.2</v>
       </c>
     </row>
@@ -5079,36 +5295,39 @@
         <v>21</v>
       </c>
       <c r="I76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" t="n">
         <v>9</v>
       </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
         <v>4</v>
       </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
         <v>13</v>
       </c>
-      <c r="P76" t="n">
+      <c r="Q76" t="n">
         <v>34</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="R76" t="n">
         <v>15.4</v>
       </c>
-      <c r="R76" t="n">
+      <c r="S76" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="S76" t="n">
+      <c r="T76" t="n">
         <v>11.2</v>
       </c>
     </row>
@@ -5141,36 +5360,39 @@
         <v>19</v>
       </c>
       <c r="I77" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" t="n">
         <v>7</v>
       </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
         <v>9</v>
       </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
         <v>16</v>
       </c>
-      <c r="P77" t="n">
+      <c r="Q77" t="n">
         <v>35</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="R77" t="n">
         <v>18.8</v>
       </c>
-      <c r="R77" t="n">
+      <c r="S77" t="n">
         <v>34.7</v>
       </c>
-      <c r="S77" t="n">
+      <c r="T77" t="n">
         <v>17.4</v>
       </c>
     </row>
@@ -5203,36 +5425,39 @@
         <v>36</v>
       </c>
       <c r="I78" t="n">
+        <v>14</v>
+      </c>
+      <c r="J78" t="n">
         <v>11</v>
       </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
       </c>
       <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
         <v>12</v>
       </c>
-      <c r="P78" t="n">
+      <c r="Q78" t="n">
         <v>48</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="R78" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="R78" t="n">
+      <c r="S78" t="n">
         <v>1.3</v>
       </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -5265,36 +5490,39 @@
         <v>27</v>
       </c>
       <c r="I79" t="n">
+        <v>8</v>
+      </c>
+      <c r="J79" t="n">
         <v>4</v>
       </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
         <v>5</v>
       </c>
-      <c r="P79" t="n">
+      <c r="Q79" t="n">
         <v>32</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
         <v>2.2</v>
       </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -5327,10 +5555,10 @@
         <v>5</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -5345,18 +5573,21 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
         <v>6</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
         <v>114</v>
       </c>
-      <c r="S80" t="n">
+      <c r="T80" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5389,7 +5620,7 @@
         <v>5</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -5410,9 +5641,12 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
         <v>5</v>
       </c>
-      <c r="S81" t="n">
+      <c r="T81" t="n">
         <v>11.3</v>
       </c>
     </row>
@@ -5445,36 +5679,39 @@
         <v>35</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
         <v>3</v>
       </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
       <c r="N82" t="n">
         <v>0</v>
       </c>
       <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
         <v>4</v>
       </c>
-      <c r="P82" t="n">
+      <c r="Q82" t="n">
         <v>39</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="R82" t="n">
         <v>25</v>
       </c>
-      <c r="R82" t="n">
+      <c r="S82" t="n">
         <v>4.4</v>
       </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5507,36 +5744,39 @@
         <v>32</v>
       </c>
       <c r="I83" t="n">
+        <v>7</v>
+      </c>
+      <c r="J83" t="n">
         <v>2</v>
       </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
         <v>4</v>
       </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
         <v>6</v>
       </c>
-      <c r="P83" t="n">
+      <c r="Q83" t="n">
         <v>38</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="R83" t="n">
         <v>33.3</v>
       </c>
-      <c r="R83" t="n">
+      <c r="S83" t="n">
         <v>176.8</v>
       </c>
-      <c r="S83" t="n">
+      <c r="T83" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -5569,36 +5809,39 @@
         <v>45</v>
       </c>
       <c r="I84" t="n">
+        <v>21</v>
+      </c>
+      <c r="J84" t="n">
         <v>2</v>
       </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
       </c>
       <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
         <v>3</v>
       </c>
-      <c r="P84" t="n">
+      <c r="Q84" t="n">
         <v>48</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
         <v>10</v>
       </c>
-      <c r="S84" t="n">
+      <c r="T84" t="n">
         <v>6.4</v>
       </c>
     </row>
@@ -5631,7 +5874,7 @@
         <v>28</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -5640,27 +5883,30 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
         <v>29</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
         <v>6.8</v>
       </c>
-      <c r="S85" t="n">
+      <c r="T85" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -5693,37 +5939,40 @@
         <v>23</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
         <v>6</v>
       </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
       <c r="N86" t="n">
         <v>0</v>
       </c>
       <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
         <v>7</v>
       </c>
-      <c r="P86" t="n">
+      <c r="Q86" t="n">
         <v>30</v>
       </c>
-      <c r="Q86" t="n">
-        <v>14.3</v>
-      </c>
       <c r="R86" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="S86" t="n">
         <v>171.3</v>
       </c>
-      <c r="S86" t="n">
-        <v>2.6</v>
+      <c r="T86" t="n">
+        <v>5.3</v>
       </c>
     </row>
     <row r="87">
@@ -5755,7 +6004,7 @@
         <v>5</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -5776,12 +6025,15 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
         <v>5</v>
       </c>
-      <c r="R87" t="n">
+      <c r="S87" t="n">
         <v>8.1</v>
       </c>
-      <c r="S87" t="n">
+      <c r="T87" t="n">
         <v>6.7</v>
       </c>
     </row>
@@ -5814,10 +6066,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -5832,15 +6084,18 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="n">
         <v>9</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
         <v>9.9</v>
       </c>
     </row>
@@ -5873,36 +6128,39 @@
         <v>42</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
         <v>2</v>
       </c>
-      <c r="P89" t="n">
+      <c r="Q89" t="n">
         <v>44</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
         <v>3</v>
       </c>
-      <c r="S89" t="n">
+      <c r="T89" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -5935,37 +6193,40 @@
         <v>65</v>
       </c>
       <c r="I90" t="n">
+        <v>33</v>
+      </c>
+      <c r="J90" t="n">
         <v>5</v>
       </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
       </c>
       <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
         <v>6</v>
       </c>
-      <c r="P90" t="n">
+      <c r="Q90" t="n">
         <v>71</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
         <v>35.8</v>
       </c>
-      <c r="S90" t="n">
-        <v>3.7</v>
+      <c r="T90" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="91">
@@ -5997,37 +6258,40 @@
         <v>55</v>
       </c>
       <c r="I91" t="n">
+        <v>21</v>
+      </c>
+      <c r="J91" t="n">
         <v>7</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
       <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>2</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
       <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
         <v>9</v>
       </c>
-      <c r="P91" t="n">
+      <c r="Q91" t="n">
         <v>64</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
         <v>20.7</v>
       </c>
-      <c r="S91" t="n">
-        <v>2.4</v>
+      <c r="T91" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="92">
@@ -6059,37 +6323,40 @@
         <v>23</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
         <v>3</v>
       </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
         <v>4</v>
       </c>
-      <c r="P92" t="n">
+      <c r="Q92" t="n">
         <v>27</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.8</v>
+        <v>13.9</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="93">
@@ -6112,44 +6379,53 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1"/>
+  <autoFilter ref="A1:T1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6160,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6182,6 +6458,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6227,55 +6504,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>No-effort closes (fast/spam/no-reply)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>CUS created</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CUS P0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CUS P1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>REP created</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>REP P0</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>REP P1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Linear total</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Grand total</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>1 Metric: created+completed ≤7d (%)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Avg 1st response (min)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Avg resolution (hrs)</t>
         </is>
@@ -6310,36 +6592,39 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>7</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>16</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>14.3</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>1.3</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>13.6</v>
       </c>
     </row>
@@ -6372,36 +6657,39 @@
         <v>44</v>
       </c>
       <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>13</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>57</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>30.3</v>
       </c>
     </row>
@@ -6434,36 +6722,39 @@
         <v>76</v>
       </c>
       <c r="I4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>9</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>13</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>89</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>7.7</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>26.7</v>
       </c>
     </row>
@@ -6496,36 +6787,39 @@
         <v>91</v>
       </c>
       <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>13</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>17</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>108</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>23.5</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>10.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>49.7</v>
       </c>
     </row>
@@ -6558,37 +6852,40 @@
         <v>135</v>
       </c>
       <c r="I6" t="n">
+        <v>29</v>
+      </c>
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>9</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>20</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>155</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>275.7</v>
       </c>
-      <c r="S6" t="n">
-        <v>32.4</v>
+      <c r="T6" t="n">
+        <v>36.9</v>
       </c>
     </row>
     <row r="7">
@@ -6620,36 +6917,39 @@
         <v>71</v>
       </c>
       <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
         <v>19</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>10</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>29</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>100</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>10.3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>28.6</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>46.4</v>
       </c>
     </row>
@@ -6682,36 +6982,39 @@
         <v>118</v>
       </c>
       <c r="I8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>19</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>35</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>153</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>8.6</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>46.9</v>
       </c>
     </row>
@@ -6744,36 +7047,39 @@
         <v>93</v>
       </c>
       <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>16</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>35</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>128</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>20</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>11.8</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>36.6</v>
       </c>
     </row>
@@ -6806,37 +7112,40 @@
         <v>138</v>
       </c>
       <c r="I10" t="n">
+        <v>42</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>11</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>21</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>159</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>14.3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>79.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>24.5</v>
+      <c r="T10" t="n">
+        <v>24.7</v>
       </c>
     </row>
     <row r="11">
@@ -6868,37 +7177,40 @@
         <v>112</v>
       </c>
       <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>14</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>24</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>136</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>12.5</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>104.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>22</v>
+      <c r="T11" t="n">
+        <v>24.1</v>
       </c>
     </row>
     <row r="12">
@@ -6930,36 +7242,39 @@
         <v>89</v>
       </c>
       <c r="I12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J12" t="n">
         <v>14</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>13</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>27</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>116</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>7.4</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>38</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -6992,36 +7307,39 @@
         <v>121</v>
       </c>
       <c r="I13" t="n">
+        <v>41</v>
+      </c>
+      <c r="J13" t="n">
         <v>32</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>16</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
         <v>48</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>169</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>14.6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>13.9</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>9.1</v>
       </c>
     </row>
@@ -7054,37 +7372,40 @@
         <v>176</v>
       </c>
       <c r="I14" t="n">
+        <v>73</v>
+      </c>
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>15</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>22</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>198</v>
       </c>
-      <c r="Q14" t="n">
-        <v>18.2</v>
-      </c>
       <c r="R14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="S14" t="n">
         <v>71.7</v>
       </c>
-      <c r="S14" t="n">
-        <v>4.9</v>
+      <c r="T14" t="n">
+        <v>5.3</v>
       </c>
     </row>
     <row r="15">
@@ -7107,50 +7428,53 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="L15" t="n">
-        <v>9</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>208</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="R15" t="n">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>20.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1"/>
+  <autoFilter ref="A1:T1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7161,7 +7485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7183,6 +7507,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7228,55 +7553,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>No-effort closes (fast/spam/no-reply)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>CUS created</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CUS P0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CUS P1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>REP created</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>REP P0</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>REP P1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Linear total</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Grand total</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>1 Metric: created+completed ≤7d (%)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Avg 1st response (min)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Avg resolution (hrs)</t>
         </is>
@@ -7311,36 +7641,39 @@
         <v>176</v>
       </c>
       <c r="I2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" t="n">
         <v>19</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>21</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>40</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>216</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>17.5</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>34.5</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>33.1</v>
       </c>
     </row>
@@ -7373,37 +7706,40 @@
         <v>443</v>
       </c>
       <c r="I3" t="n">
+        <v>111</v>
+      </c>
+      <c r="J3" t="n">
         <v>63</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>58</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>121</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>564</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>10.7</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>117.2</v>
       </c>
-      <c r="S3" t="n">
-        <v>41.6</v>
+      <c r="T3" t="n">
+        <v>42.9</v>
       </c>
     </row>
     <row r="4">
@@ -7435,37 +7771,40 @@
         <v>478</v>
       </c>
       <c r="I4" t="n">
+        <v>146</v>
+      </c>
+      <c r="J4" t="n">
         <v>68</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>60</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
         <v>128</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>606</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>14.1</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>62.1</v>
       </c>
-      <c r="S4" t="n">
-        <v>19</v>
+      <c r="T4" t="n">
+        <v>19.6</v>
       </c>
     </row>
     <row r="5">
@@ -7488,50 +7827,53 @@
         <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G5" t="n">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>24</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>406</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.9</v>
+        <v>424</v>
       </c>
       <c r="R5" t="n">
-        <v>45.7</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>45.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1"/>
+  <autoFilter ref="A1:T1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>